--- a/17_Real_Estate_REIT/_template_REAL_ESTATE.xlsx
+++ b/17_Real_Estate_REIT/_template_REAL_ESTATE.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Property Pro Forma" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Cap Rate &amp; Valuation" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="REIT FFO-AFFO" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="RefreshLog" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="5-Year Hold &amp; IRR" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="RefreshLog" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
   <si>
     <t xml:space="preserve">[PROPERTY/REIT] — Real Estate Model</t>
   </si>
@@ -144,6 +145,84 @@
   </si>
   <si>
     <t xml:space="preserve">AFFO / share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-Year Hold — Levered Cash Flow &amp; IRR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumptions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOI growth rate (%/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exit cap rate (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selling costs (% of exit value)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual debt service ($, assumed constant / interest-only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initial equity (purchase price - debt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yr1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yr2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yr3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yr4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yr5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levered cash flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSCR (NOI / debt service)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exit (end of Yr5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forward NOI (Yr6, for exit cap)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exit value (forward NOI / exit cap rate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less: selling costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less: debt payoff (assumed interest-only, balance unchanged)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net exit equity proceeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yr0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity cash flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levered IRR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equity multiple (MOIC)</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -168,12 +247,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="168" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
+    <numFmt numFmtId="169" formatCode="0.0\x"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -250,7 +330,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -261,6 +341,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
     <fill>
@@ -319,7 +405,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -376,8 +462,32 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -418,7 +528,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -637,7 +747,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C7"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -699,7 +809,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -812,7 +922,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
@@ -902,7 +1012,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D15"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
@@ -1018,8 +1128,319 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:H28"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <f aca="false">IFERROR(ABS('Property Pro Forma'!C13),"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <f aca="false">IFERROR('Cap Rate &amp; Valuation'!C8-'Cap Rate &amp; Valuation'!C10,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <f aca="false">'Property Pro Forma'!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <f aca="false">C13*(1+$C$5)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <f aca="false">D13*(1+$C$5)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <f aca="false">E13*(1+$C$5)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <f aca="false">F13*(1+$C$5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <f aca="false">$C$8</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <f aca="false">$C$8</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <f aca="false">$C$8</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <f aca="false">$C$8</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <f aca="false">$C$8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <f aca="false">C13-C14</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <f aca="false">D13-D14</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <f aca="false">E13-E14</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <f aca="false">F13-F14</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <f aca="false">G13-G14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="18" t="str">
+        <f aca="false">IFERROR(C13/C14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D16" s="18" t="str">
+        <f aca="false">IFERROR(D13/D14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E16" s="18" t="str">
+        <f aca="false">IFERROR(E13/E14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F16" s="18" t="str">
+        <f aca="false">IFERROR(F13/F14,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G16" s="18" t="str">
+        <f aca="false">IFERROR(G13/G14,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <f aca="false">G13*(1+$C$5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <f aca="false">IFERROR(C19/C6,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <f aca="false">-C20*C7</f>
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <f aca="false">-'Cap Rate &amp; Valuation'!C10</f>
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <f aca="false">C20+C21+C22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="14"/>
+      <c r="C25" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <f aca="false">-C9</f>
+        <v>-0</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <f aca="false">C15</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <f aca="false">D15</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <f aca="false">E15</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <f aca="false">F15</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <f aca="false">G15+C23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="19" t="str">
+        <f aca="false">IFERROR(IRR(C26:H26),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="20" t="str">
+        <f aca="false">IFERROR(SUM(D26:H26)/C9,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
@@ -1030,95 +1451,95 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>45</v>
+      <c r="B4" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/17_Real_Estate_REIT/_template_REAL_ESTATE.xlsx
+++ b/17_Real_Estate_REIT/_template_REAL_ESTATE.xlsx
@@ -770,11 +770,11 @@
         </is>
       </c>
       <c r="C9" s="21">
-        <f>IFERROR('Cap Rate &amp; Valuation'!C10/'Cap Rate &amp; Valuation'!C8,0)</f>
+        <f>IFERROR('Cap Rate &amp; Valuation'!C10/'Cap Rate &amp; Valuation'!C8,"-")</f>
         <v/>
       </c>
       <c r="D9" s="21">
-        <f>IF(C9&lt;=0.75,"PASS",IF(C9&lt;=0.85,"REVIEW","BREACH"))</f>
+        <f>IF(ISNUMBER(C9),IF(C9&lt;=0.75,"PASS",IF(C9&lt;=0.85,"REVIEW","BREACH")),"REVIEW")</f>
         <v/>
       </c>
       <c r="E9" t="inlineStr">
